--- a/artfynd/A 61301-2021 artfynd.xlsx
+++ b/artfynd/A 61301-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 61301-2021 artfynd.xlsx
+++ b/artfynd/A 61301-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1948,862 +1948,6 @@
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>112606459</v>
-      </c>
-      <c r="B13" t="n">
-        <v>78919</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Tallsjö, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q13" t="n">
-        <v>641958</v>
-      </c>
-      <c r="R13" t="n">
-        <v>7120727</v>
-      </c>
-      <c r="S13" t="n">
-        <v>10</v>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>Åsele</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>Fredrika</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>2022-10-04</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>2022-10-04</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT13" t="inlineStr"/>
-      <c r="AW13" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>112606463</v>
-      </c>
-      <c r="B14" t="n">
-        <v>89789</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Tallsjö, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q14" t="n">
-        <v>642479</v>
-      </c>
-      <c r="R14" t="n">
-        <v>7120911</v>
-      </c>
-      <c r="S14" t="n">
-        <v>10</v>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>Åsele</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>Fredrika</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>2022-10-04</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>2022-10-04</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT14" t="inlineStr"/>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>112606465</v>
-      </c>
-      <c r="B15" t="n">
-        <v>89789</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Tallsjö, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q15" t="n">
-        <v>642432</v>
-      </c>
-      <c r="R15" t="n">
-        <v>7120662</v>
-      </c>
-      <c r="S15" t="n">
-        <v>10</v>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>Åsele</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>Fredrika</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>2022-10-04</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>2022-10-04</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT15" t="inlineStr"/>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>112606471</v>
-      </c>
-      <c r="B16" t="n">
-        <v>78919</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Tallsjö, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q16" t="n">
-        <v>642519</v>
-      </c>
-      <c r="R16" t="n">
-        <v>7120997</v>
-      </c>
-      <c r="S16" t="n">
-        <v>10</v>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>Åsele</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>Fredrika</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>2022-10-04</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>2022-10-04</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="inlineStr"/>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>112606462</v>
-      </c>
-      <c r="B17" t="n">
-        <v>89789</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Tallsjö, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q17" t="n">
-        <v>641895</v>
-      </c>
-      <c r="R17" t="n">
-        <v>7120763</v>
-      </c>
-      <c r="S17" t="n">
-        <v>10</v>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>Åsele</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>Fredrika</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>2022-10-04</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>2022-10-04</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT17" t="inlineStr"/>
-      <c r="AW17" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>112606469</v>
-      </c>
-      <c r="B18" t="n">
-        <v>78920</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>2081</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Skrovellav</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Lobaria scrobiculata</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Tallsjö, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q18" t="n">
-        <v>642589</v>
-      </c>
-      <c r="R18" t="n">
-        <v>7121015</v>
-      </c>
-      <c r="S18" t="n">
-        <v>10</v>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>Åsele</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>Fredrika</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>2022-10-04</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>2022-10-04</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT18" t="inlineStr"/>
-      <c r="AW18" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>112606468</v>
-      </c>
-      <c r="B19" t="n">
-        <v>78919</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>Tallsjö, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q19" t="n">
-        <v>642654</v>
-      </c>
-      <c r="R19" t="n">
-        <v>7120928</v>
-      </c>
-      <c r="S19" t="n">
-        <v>10</v>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>Åsele</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>Fredrika</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>2022-10-04</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>2022-10-04</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT19" t="inlineStr"/>
-      <c r="AW19" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>112606466</v>
-      </c>
-      <c r="B20" t="n">
-        <v>89767</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>1108</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Harticka</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>Tallsjö, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q20" t="n">
-        <v>642442</v>
-      </c>
-      <c r="R20" t="n">
-        <v>7120639</v>
-      </c>
-      <c r="S20" t="n">
-        <v>10</v>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>Åsele</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>Fredrika</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>2022-10-04</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>2022-10-04</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT20" t="inlineStr"/>
-      <c r="AW20" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 61301-2021 artfynd.xlsx
+++ b/artfynd/A 61301-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104159780</v>
+        <v>112606466</v>
       </c>
       <c r="B2" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6462</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>641958.4914713959</v>
+        <v>642443</v>
       </c>
       <c r="R2" t="n">
-        <v>7120726.662809556</v>
+        <v>7120639</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,24 +743,14 @@
           <t>2022-10-04</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-10-04</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Påträffad i samband med Sveaskogs naturvärdesbedömning</t>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104159787</v>
+        <v>112606469</v>
       </c>
       <c r="B3" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>642653.775508886</v>
+        <v>642589</v>
       </c>
       <c r="R3" t="n">
-        <v>7120927.619084193</v>
+        <v>7121016</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,24 +845,14 @@
           <t>2022-10-04</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-10-04</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Påträffad i samband med Sveaskogs naturvärdesbedömning</t>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,15 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104159784</v>
+        <v>112181642</v>
       </c>
       <c r="B4" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,37 +890,41 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Tallsjö, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>642479.272418197</v>
+        <v>642374</v>
       </c>
       <c r="R4" t="n">
-        <v>7120911.271845043</v>
+        <v>7120796</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,27 +948,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-10-04</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-10-04</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-25</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Påträffad i samband med Sveaskogs naturvärdesbedömning</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,15 +985,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104159785</v>
+        <v>112606459</v>
       </c>
       <c r="B5" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1042,21 +996,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,10 +1020,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>642432.2188025683</v>
+        <v>641958</v>
       </c>
       <c r="R5" t="n">
-        <v>7120661.600530208</v>
+        <v>7120727</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,24 +1053,14 @@
           <t>2022-10-04</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-10-04</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Påträffad i samband med Sveaskogs naturvärdesbedömning</t>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,15 +1087,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>104159781</v>
+        <v>112606468</v>
       </c>
       <c r="B6" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,10 +1122,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>641958.4914713959</v>
+        <v>642654</v>
       </c>
       <c r="R6" t="n">
-        <v>7120726.662809556</v>
+        <v>7120927</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1216,24 +1155,14 @@
           <t>2022-10-04</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-10-04</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Påträffad i samband med Sveaskogs naturvärdesbedömning</t>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1260,15 +1189,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>104159789</v>
+        <v>112606471</v>
       </c>
       <c r="B7" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,10 +1224,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>642519.0262410669</v>
+        <v>642519</v>
       </c>
       <c r="R7" t="n">
-        <v>7120996.911387253</v>
+        <v>7120997</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1333,24 +1257,14 @@
           <t>2022-10-04</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-10-04</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Påträffad i samband med Sveaskogs naturvärdesbedömning</t>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1374,579 +1288,6 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>104159788</v>
-      </c>
-      <c r="B8" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>2081</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Skrovellav</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Lobaria scrobiculata</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Tallsjö, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>642588.5364200586</v>
-      </c>
-      <c r="R8" t="n">
-        <v>7121015.396162445</v>
-      </c>
-      <c r="S8" t="n">
-        <v>10</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Åsele</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Fredrika</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2022-10-04</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2022-10-04</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Påträffad i samband med Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>104159786</v>
-      </c>
-      <c r="B9" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>1108</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Harticka</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Tallsjö, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>642442.4426213912</v>
-      </c>
-      <c r="R9" t="n">
-        <v>7120638.935859701</v>
-      </c>
-      <c r="S9" t="n">
-        <v>10</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Åsele</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Fredrika</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2022-10-04</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2022-10-04</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Påträffad i samband med Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>104159782</v>
-      </c>
-      <c r="B10" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Tallsjö, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q10" t="n">
-        <v>641895.1937866264</v>
-      </c>
-      <c r="R10" t="n">
-        <v>7120763.04050907</v>
-      </c>
-      <c r="S10" t="n">
-        <v>10</v>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Åsele</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>Fredrika</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>2022-10-04</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>2022-10-04</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Påträffad i samband med Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>112181558</v>
-      </c>
-      <c r="B11" t="n">
-        <v>89610</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Tallsjö, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q11" t="n">
-        <v>642381</v>
-      </c>
-      <c r="R11" t="n">
-        <v>7120689</v>
-      </c>
-      <c r="S11" t="n">
-        <v>5</v>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>Åsele</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>Fredrika</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>2023-08-25</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>2023-08-25</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
-        </is>
-      </c>
-      <c r="AD11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT11" t="inlineStr"/>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>112181642</v>
-      </c>
-      <c r="B12" t="n">
-        <v>78752</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Tallsjö, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q12" t="n">
-        <v>642374</v>
-      </c>
-      <c r="R12" t="n">
-        <v>7120796</v>
-      </c>
-      <c r="S12" t="n">
-        <v>5</v>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>Åsele</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>Fredrika</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>2023-08-25</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>2023-08-25</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
-        </is>
-      </c>
-      <c r="AD12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="inlineStr"/>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 61301-2021 artfynd.xlsx
+++ b/artfynd/A 61301-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606466</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606469</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -982,6 +997,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112181642</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1084,6 +1104,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606459</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1186,6 +1211,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606468</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1288,8 +1318,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606471</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>